--- a/tests/AustinS/runlog_results.xlsx
+++ b/tests/AustinS/runlog_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AK36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4779,6 +4779,129 @@
       </c>
       <c r="AK35" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>runlog_20260215_185838.txt</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>15-Feb-2026 18:58:38</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>13</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>QPSK</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Chase Combining</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>[0 2 3 1]</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>TDL-C</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="M36" t="n">
+        <v>20</v>
+      </c>
+      <c r="N36" t="n">
+        <v>20</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>20</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>240800</v>
+      </c>
+      <c r="V36" t="n">
+        <v>240800</v>
+      </c>
+      <c r="W36" t="n">
+        <v>100</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>12040</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>6666.69</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>16.32</v>
       </c>
     </row>
   </sheetData>
